--- a/sheets/조재수대금교본/검수/주안에우린하나.xlsx
+++ b/sheets/조재수대금교본/검수/주안에우린하나.xlsx
@@ -4445,8 +4445,7 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -4490,14 +4489,14 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄴ
+          <t xml:space="preserve">林
 潢</t>
         </is>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄴ
+          <t xml:space="preserve">林
 潢</t>
         </is>
       </c>
@@ -4522,38 +4521,27 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
@@ -4606,15 +4594,13 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="O7" s="22"/>
@@ -4680,8 +4666,7 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E9" s="23"/>
@@ -4720,11 +4705,7 @@
     </row>
     <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="24"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
@@ -4733,23 +4714,11 @@
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -4804,15 +4773,13 @@
       <c r="K11" s="22"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="M11" s="22"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃
-‹</t>
+          <t xml:space="preserve">黃</t>
         </is>
       </c>
       <c r="O11" s="22"/>
@@ -4821,16 +4788,14 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -4851,8 +4816,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K12" s="23"/>
@@ -4902,16 +4866,14 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-姑
-‹</t>
+姑</t>
         </is>
       </c>
       <c r="M13" s="23"/>
@@ -4939,11 +4901,7 @@
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
@@ -4966,11 +4924,7 @@
         </is>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
     </row>
     <row r="15" ht="91.25" customHeight="true">
@@ -5109,17 +5063,9 @@
         </is>
       </c>
       <c r="E18" s="24"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
       <c r="J18" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/주안에우린하나.xlsx
+++ b/sheets/조재수대금교본/검수/주안에우린하나.xlsx
@@ -4489,14 +4489,14 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄴ
 潢</t>
         </is>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
+          <t xml:space="preserve">林ㄴ
 潢</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/주안에우린하나.xlsx
+++ b/sheets/조재수대금교본/검수/주안에우린하나.xlsx
@@ -4324,26 +4324,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
       <c r="N14" s="21"/>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5090,6 +5090,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>